--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Proyecto ING2530001 DECANAT FACULTAD DE INGENIERÍA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +822,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1537,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1602,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1667,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1729,7 +1793,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1858,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1981,7 +2053,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2042,7 +2118,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2103,7 +2183,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2164,7 +2248,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2225,7 +2313,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2286,7 +2378,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2347,7 +2443,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2408,7 +2508,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2469,7 +2573,11 @@
           <t>76.486.150-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2652,7 +2760,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2774,7 +2886,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2896,7 +3012,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2957,7 +3077,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3018,7 +3142,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3079,7 +3207,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3140,7 +3272,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3262,7 +3398,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3323,7 +3463,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3445,7 +3589,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3506,7 +3654,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/mar-2026.xlsx
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
